--- a/data/trans_bre/IP1012-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1012-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 0,0</t>
+          <t>-7,44; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; -0,28</t>
+          <t>-1,78; -0,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,73</t>
+          <t>-0,9; 0,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,0</t>
+          <t>-0,64; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,14</t>
+          <t>-2,52; 1,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,69</t>
+          <t>-1,49; 1,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; -0,35</t>
+          <t>-3,38; -0,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,27 +874,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,07</t>
+          <t>-1,15; 0,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,34</t>
+          <t>-1,13; 0,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,89; -0,1</t>
+          <t>-0,9; -0,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-92,39; 75,3</t>
+          <t>-100,0; 64,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,48; 99,8</t>
+          <t>-90,55; 84,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP1012-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1012-Estudios-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 0,0</t>
+          <t>-6,84; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,78; -0,27</t>
+          <t>-1,74; -0,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,86</t>
+          <t>-0,9; 0,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,0</t>
+          <t>-0,63; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 348,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,1</t>
+          <t>-2,53; 1,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,67</t>
+          <t>-1,56; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,34</t>
+          <t>-3,06; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,27 +874,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,09</t>
+          <t>-1,17; 0,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,27</t>
+          <t>-1,05; 0,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,9; -0,09</t>
+          <t>-0,99; -0,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 64,21</t>
+          <t>-92,64; 57,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,55; 84,86</t>
+          <t>-86,8; 136,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP1012-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1012-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 0,0</t>
+          <t>-7,53; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; -0,28</t>
+          <t>-1,89; -0,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,71</t>
+          <t>-0,91; 0,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,0</t>
+          <t>-0,76; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 348,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,15</t>
+          <t>-2,46; 1,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,44</t>
+          <t>-1,51; 1,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,0</t>
+          <t>-3,12; -0,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,27 +874,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,11</t>
+          <t>-1,15; 0,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,36</t>
+          <t>-1,03; 0,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,99; -0,1</t>
+          <t>-0,89; -0,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-92,64; 57,48</t>
+          <t>-92,39; 75,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,8; 136,26</t>
+          <t>-85,48; 99,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP1012-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1012-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,135 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.7064589993198428</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.171058755358308</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,59</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,53; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.528164882356473</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.59095113660523</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-14,53%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,89; -0,28</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,91; 0,73</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; 0,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.780603651904999</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.08759538938584113</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.1264224437452385</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1452704732897754</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.999976897542739</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-36,83%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-24,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.891316090925759</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.9064082093200452</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.7566793235674705</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,46; 1,14</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,51; 1,69</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,12; -0,35</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-0.2808999517804647</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.7302979562454247</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.952758482929638e-06</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +739,145 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-62,57%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-43,46%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.4578970510935452</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.181607373306438</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.129591797950212</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.3683047473628734</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2449608227952674</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,15; 0,07</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,03; 0,34</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; -0,1</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-92,39; 75,3</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-85,48; 99,8</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.463585717564989</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.509466169871054</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.121173972431547</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.139834964248085</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.694631492863267</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-0.3452756700784468</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.4930482174717769</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.3526760733814782</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3672980906298767</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.6256605873386141</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.4346242744691424</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.9999946681400167</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.154460582856498</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.026212316088462</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.8891383266096509</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.9238885947732566</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8547784405718756</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.07262125485878926</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.3380361407303851</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-0.09645201821328275</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.7529997692871422</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.9979864220528105</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +886,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
